--- a/dataset/Task01/tc01_output01.xlsx
+++ b/dataset/Task01/tc01_output01.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Merged Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,18 +17,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,12 +37,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FF0000"/>
+        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,22 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -438,38 +424,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Daily Spending (£)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total Spending (£)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,12 +461,9 @@
       <c r="C2" t="n">
         <v>106.11</v>
       </c>
-      <c r="E2" t="n">
-        <v>106.11</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="1" t="n">
         <v>45963</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -496,12 +474,9 @@
       <c r="C3" t="n">
         <v>43.62</v>
       </c>
-      <c r="E3" t="n">
-        <v>43.62</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="1" t="n">
         <v>45964</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -517,12 +492,9 @@
           <t>Gift</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>89.53</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -530,17 +502,17 @@
           <t>Entertainment</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v/>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Gift</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="1" t="n">
         <v>45966</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -556,12 +528,9 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>61.14</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="1" t="n">
         <v>45967</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -577,12 +546,9 @@
           <t>Bus fare</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>92.15000000000001</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -598,28 +564,23 @@
           <t>Coffee</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>76.3</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>45969</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="3" t="n">
         <v>116.58</v>
       </c>
-      <c r="E9" t="n">
-        <v>116.58</v>
-      </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="1" t="n">
         <v>45970</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -635,12 +596,9 @@
           <t>Groceries</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>32.59</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="1" t="n">
         <v>45971</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -656,12 +614,9 @@
           <t>Clothes</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>58.96</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="1" t="n">
         <v>45972</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -677,12 +632,9 @@
           <t>Groceries</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>56.22</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="1" t="n">
         <v>45973</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,12 +650,9 @@
           <t>Gift</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>93.13</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="1" t="n">
         <v>45974</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -719,12 +668,9 @@
           <t>Bus fare</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>67.38</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -740,12 +686,9 @@
           <t>Groceries</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>73.28</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="1" t="n">
         <v>45976</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -761,12 +704,9 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>67.03</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="1" t="n">
         <v>45977</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -782,12 +722,9 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>51.77</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="1" t="n">
         <v>45978</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,12 +740,9 @@
           <t>Groceries</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>101.05</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="1" t="n">
         <v>45979</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -824,12 +758,9 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>42.52</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="1" t="n">
         <v>45980</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -840,12 +771,9 @@
       <c r="C20" t="n">
         <v>107.96</v>
       </c>
-      <c r="E20" t="n">
-        <v>107.96</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="1" t="n">
         <v>45981</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -861,12 +789,9 @@
           <t>Coffee</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>22.64</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -874,17 +799,17 @@
           <t>Shopping</t>
         </is>
       </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>Coffee</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="1" t="n">
         <v>45983</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -900,12 +825,9 @@
           <t>Cinema</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>38.45</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="1" t="n">
         <v>45984</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -916,12 +838,9 @@
       <c r="C24" t="n">
         <v>115.04</v>
       </c>
-      <c r="E24" t="n">
-        <v>115.04</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="1" t="n">
         <v>45985</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -937,12 +856,9 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>71.52</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="1" t="n">
         <v>45986</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -958,12 +874,9 @@
           <t>Lunch</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>111.18</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -974,12 +887,9 @@
       <c r="C27" t="n">
         <v>102.98</v>
       </c>
-      <c r="E27" t="n">
-        <v>102.98</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="1" t="n">
         <v>45988</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -995,12 +905,9 @@
           <t>Groceries</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>57.13</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1016,12 +923,9 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>32.5</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="1" t="n">
         <v>45990</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1037,12 +941,9 @@
           <t>Gift</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>99.25</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1058,274 +959,59 @@
           <t>Dinner</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>35.74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Total Spending (£)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B2" t="n">
-        <v>106.11</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>45963</v>
-      </c>
-      <c r="B3" t="n">
-        <v>43.62</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>45964</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89.53</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B6" t="n">
-        <v>61.14</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B7" t="n">
-        <v>92.15000000000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>45968</v>
-      </c>
-      <c r="B8" t="n">
-        <v>76.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>45969</v>
-      </c>
-      <c r="B9" s="5" t="n">
+      <c r="B34" t="n">
+        <v>2023.75</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Average Daily Spending (£)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>69.78448275862068</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Max Spending Day(s)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-11-08 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Max Spending Amount (£)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>116.58</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>45970</v>
-      </c>
-      <c r="B10" t="n">
-        <v>32.59</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>45971</v>
-      </c>
-      <c r="B11" t="n">
-        <v>58.96</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>45972</v>
-      </c>
-      <c r="B12" t="n">
-        <v>56.22</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>45973</v>
-      </c>
-      <c r="B13" t="n">
-        <v>93.13</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>45974</v>
-      </c>
-      <c r="B14" t="n">
-        <v>67.38</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>45975</v>
-      </c>
-      <c r="B15" t="n">
-        <v>73.28</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B16" t="n">
-        <v>67.03</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>45977</v>
-      </c>
-      <c r="B17" t="n">
-        <v>51.77</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>45978</v>
-      </c>
-      <c r="B18" t="n">
-        <v>101.05</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>45979</v>
-      </c>
-      <c r="B19" t="n">
-        <v>42.52</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>45980</v>
-      </c>
-      <c r="B20" t="n">
-        <v>107.96</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>45981</v>
-      </c>
-      <c r="B21" t="n">
-        <v>22.64</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>45982</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>45983</v>
-      </c>
-      <c r="B23" t="n">
-        <v>38.45</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>45984</v>
-      </c>
-      <c r="B24" t="n">
-        <v>115.04</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>45985</v>
-      </c>
-      <c r="B25" t="n">
-        <v>71.52</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>45986</v>
-      </c>
-      <c r="B26" t="n">
-        <v>111.18</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>45987</v>
-      </c>
-      <c r="B27" t="n">
-        <v>102.98</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>45988</v>
-      </c>
-      <c r="B28" t="n">
-        <v>57.13</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>45989</v>
-      </c>
-      <c r="B29" t="n">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>45990</v>
-      </c>
-      <c r="B30" t="n">
-        <v>99.25</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>45991</v>
-      </c>
-      <c r="B31" t="n">
-        <v>35.74</v>
       </c>
     </row>
   </sheetData>
